--- a/outputs/M7b_human_capital_robustness_from_M4_regression_detail.xlsx
+++ b/outputs/M7b_human_capital_robustness_from_M4_regression_detail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>variable</t>
   </si>
@@ -40,19 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp</t>
+  </si>
+  <si>
+    <t>ln_gdppc</t>
+  </si>
+  <si>
+    <t>xr_dep_pct</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp</t>
   </si>
   <si>
     <t>real_interest_rate_pct</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp</t>
-  </si>
-  <si>
-    <t>ln_gdppc</t>
-  </si>
-  <si>
-    <t>xr_dep_pct</t>
   </si>
   <si>
     <t>hc_human_capital_index</t>
@@ -413,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,22 +447,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>-31.75995613712182</v>
+        <v>-24.30611104607596</v>
       </c>
       <c r="C2">
-        <v>15.0576472415545</v>
+        <v>14.9067408545135</v>
       </c>
       <c r="D2">
-        <v>-2.109224344788345</v>
+        <v>-1.630544951663025</v>
       </c>
       <c r="E2">
-        <v>0.03925278211772287</v>
+        <v>0.1085004403202763</v>
       </c>
       <c r="F2">
-        <v>-61.90111189063273</v>
+        <v>-54.15634471784136</v>
       </c>
       <c r="G2">
-        <v>-1.618800383610896</v>
+        <v>5.544122625689447</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.001677739548191352</v>
+        <v>-0.1958588857649306</v>
       </c>
       <c r="C3">
-        <v>0.0253709352400181</v>
+        <v>0.1333228264911614</v>
       </c>
       <c r="D3">
-        <v>0.06612840765700344</v>
+        <v>-1.469057406894347</v>
       </c>
       <c r="E3">
-        <v>0.9475030127992865</v>
+        <v>0.1473149989608231</v>
       </c>
       <c r="F3">
-        <v>-0.04910770511086938</v>
+        <v>-0.4628332407485294</v>
       </c>
       <c r="G3">
-        <v>0.05246318420725209</v>
+        <v>0.07111546921866818</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.00369738364175269</v>
+        <v>-0.03194384799251933</v>
       </c>
       <c r="C4">
-        <v>0.06105071115804583</v>
+        <v>0.02241365868521881</v>
       </c>
       <c r="D4">
-        <v>-0.06056249913585837</v>
+        <v>-1.425195611352172</v>
       </c>
       <c r="E4">
-        <v>0.9519158444974885</v>
+        <v>0.1595537044488353</v>
       </c>
       <c r="F4">
-        <v>-0.1259036595863137</v>
+        <v>-0.07682642532600789</v>
       </c>
       <c r="G4">
-        <v>0.1185088923028083</v>
+        <v>0.01293872934096921</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-0.03332285773467279</v>
+        <v>3.602659498925301</v>
       </c>
       <c r="C5">
-        <v>0.02149761658346632</v>
+        <v>1.661211582615125</v>
       </c>
       <c r="D5">
-        <v>-1.550072195459156</v>
+        <v>2.168693944003145</v>
       </c>
       <c r="E5">
-        <v>0.1265640370247474</v>
+        <v>0.03429284760550333</v>
       </c>
       <c r="F5">
-        <v>-0.07635501271724787</v>
+        <v>0.2761406841643645</v>
       </c>
       <c r="G5">
-        <v>0.009709297247902308</v>
+        <v>6.929178313686236</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>4.33738204581072</v>
+        <v>0.1370235736840049</v>
       </c>
       <c r="C6">
-        <v>1.483078728025243</v>
+        <v>0.035457740070048</v>
       </c>
       <c r="D6">
-        <v>2.924579770344393</v>
+        <v>3.864419261163009</v>
       </c>
       <c r="E6">
-        <v>0.004914382283542462</v>
+        <v>0.0002875214757385169</v>
       </c>
       <c r="F6">
-        <v>1.368677425558714</v>
+        <v>0.0660206739292151</v>
       </c>
       <c r="G6">
-        <v>7.306086666062727</v>
+        <v>0.2080264734387947</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.1138444586832337</v>
+        <v>-0.01100776718043064</v>
       </c>
       <c r="C7">
-        <v>0.03903441304944032</v>
+        <v>0.02995505967399102</v>
       </c>
       <c r="D7">
-        <v>2.916515192351945</v>
+        <v>-0.3674760558059686</v>
       </c>
       <c r="E7">
-        <v>0.005026285693539245</v>
+        <v>0.7146248926087049</v>
       </c>
       <c r="F7">
-        <v>0.03570859159882205</v>
+        <v>-0.07099173950859859</v>
       </c>
       <c r="G7">
-        <v>0.1919803257676453</v>
+        <v>0.0489762051477373</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +585,45 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.56386938386382</v>
+        <v>-0.1919727512167083</v>
       </c>
       <c r="C8">
-        <v>2.109315798923813</v>
+        <v>0.1167228625935871</v>
       </c>
       <c r="D8">
-        <v>0.2673233586699108</v>
+        <v>-1.644688512182321</v>
       </c>
       <c r="E8">
-        <v>0.7901684910980447</v>
+        <v>0.1055386259832913</v>
       </c>
       <c r="F8">
-        <v>-3.658384930425753</v>
+        <v>-0.4257062518699368</v>
       </c>
       <c r="G8">
-        <v>4.786123698153394</v>
+        <v>0.04176074943652028</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>1.127570030042016</v>
+      </c>
+      <c r="C9">
+        <v>2.425367318296102</v>
+      </c>
+      <c r="D9">
+        <v>0.4649069118463137</v>
+      </c>
+      <c r="E9">
+        <v>0.6437692844799305</v>
+      </c>
+      <c r="F9">
+        <v>-3.729144250939185</v>
+      </c>
+      <c r="G9">
+        <v>5.984284311023217</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M7b_human_capital_robustness_from_M4_regression_detail.xlsx
+++ b/outputs/M7b_human_capital_robustness_from_M4_regression_detail.xlsx
@@ -52,7 +52,7 @@
     <t>xr_dep_pct</t>
   </si>
   <si>
-    <t>broad_money_pct_gdp</t>
+    <t>broad_money_growth_pct</t>
   </si>
   <si>
     <t>real_interest_rate_pct</t>
@@ -447,22 +447,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>-24.30611104607596</v>
+        <v>-28.14154744620001</v>
       </c>
       <c r="C2">
-        <v>14.9067408545135</v>
+        <v>14.56033637511415</v>
       </c>
       <c r="D2">
-        <v>-1.630544951663025</v>
+        <v>-1.932753936529807</v>
       </c>
       <c r="E2">
-        <v>0.1085004403202763</v>
+        <v>0.05572547117599402</v>
       </c>
       <c r="F2">
-        <v>-54.15634471784136</v>
+        <v>-56.98277153850118</v>
       </c>
       <c r="G2">
-        <v>5.544122625689447</v>
+        <v>0.6996766461011532</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>-0.1958588857649306</v>
+        <v>0.06946676336472117</v>
       </c>
       <c r="C3">
-        <v>0.1333228264911614</v>
+        <v>0.1534034092846817</v>
       </c>
       <c r="D3">
-        <v>-1.469057406894347</v>
+        <v>0.4528371545889617</v>
       </c>
       <c r="E3">
-        <v>0.1473149989608231</v>
+        <v>0.6515191851269639</v>
       </c>
       <c r="F3">
-        <v>-0.4628332407485294</v>
+        <v>-0.2343958665717945</v>
       </c>
       <c r="G3">
-        <v>0.07111546921866818</v>
+        <v>0.3733293933012368</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.03194384799251933</v>
+        <v>-0.01646549039546036</v>
       </c>
       <c r="C4">
-        <v>0.02241365868521881</v>
+        <v>0.01735126823336982</v>
       </c>
       <c r="D4">
-        <v>-1.425195611352172</v>
+        <v>-0.9489502538952201</v>
       </c>
       <c r="E4">
-        <v>0.1595537044488353</v>
+        <v>0.3446358543172012</v>
       </c>
       <c r="F4">
-        <v>-0.07682642532600789</v>
+        <v>-0.05083501335919906</v>
       </c>
       <c r="G4">
-        <v>0.01293872934096921</v>
+        <v>0.01790403256827834</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>3.602659498925301</v>
+        <v>1.249474219573725</v>
       </c>
       <c r="C5">
-        <v>1.661211582615125</v>
+        <v>0.5319448505891041</v>
       </c>
       <c r="D5">
-        <v>2.168693944003145</v>
+        <v>2.348879246015806</v>
       </c>
       <c r="E5">
-        <v>0.03429284760550333</v>
+        <v>0.02053671982656313</v>
       </c>
       <c r="F5">
-        <v>0.2761406841643645</v>
+        <v>0.1957938480949628</v>
       </c>
       <c r="G5">
-        <v>6.929178313686236</v>
+        <v>2.303154591052488</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.1370235736840049</v>
+        <v>0.06181842390009441</v>
       </c>
       <c r="C6">
-        <v>0.035457740070048</v>
+        <v>0.03439795272743125</v>
       </c>
       <c r="D6">
-        <v>3.864419261163009</v>
+        <v>1.797154161759058</v>
       </c>
       <c r="E6">
-        <v>0.0002875214757385169</v>
+        <v>0.07493569329762373</v>
       </c>
       <c r="F6">
-        <v>0.0660206739292151</v>
+        <v>-0.00631730025967446</v>
       </c>
       <c r="G6">
-        <v>0.2080264734387947</v>
+        <v>0.1299541480598633</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>-0.01100776718043064</v>
+        <v>0.04936455774899803</v>
       </c>
       <c r="C7">
-        <v>0.02995505967399102</v>
+        <v>0.04323803096526915</v>
       </c>
       <c r="D7">
-        <v>-0.3674760558059686</v>
+        <v>1.1416930106889</v>
       </c>
       <c r="E7">
-        <v>0.7146248926087049</v>
+        <v>0.2559533411352128</v>
       </c>
       <c r="F7">
-        <v>-0.07099173950859859</v>
+        <v>-0.03628166004790419</v>
       </c>
       <c r="G7">
-        <v>0.0489762051477373</v>
+        <v>0.1350107755459002</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.1919727512167083</v>
+        <v>0.07425127276174019</v>
       </c>
       <c r="C8">
-        <v>0.1167228625935871</v>
+        <v>0.1379679108558107</v>
       </c>
       <c r="D8">
-        <v>-1.644688512182321</v>
+        <v>0.5381778436823593</v>
       </c>
       <c r="E8">
-        <v>0.1055386259832913</v>
+        <v>0.5914943662710286</v>
       </c>
       <c r="F8">
-        <v>-0.4257062518699368</v>
+        <v>-0.1990366054867369</v>
       </c>
       <c r="G8">
-        <v>0.04176074943652028</v>
+        <v>0.3475391510102173</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -608,22 +608,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1.127570030042016</v>
+        <v>0.7949309526778411</v>
       </c>
       <c r="C9">
-        <v>2.425367318296102</v>
+        <v>3.222271793362856</v>
       </c>
       <c r="D9">
-        <v>0.4649069118463137</v>
+        <v>0.24669891419936</v>
       </c>
       <c r="E9">
-        <v>0.6437692844799305</v>
+        <v>0.8055810852054184</v>
       </c>
       <c r="F9">
-        <v>-3.729144250939185</v>
+        <v>-5.587769314983435</v>
       </c>
       <c r="G9">
-        <v>5.984284311023217</v>
+        <v>7.177631220339117</v>
       </c>
     </row>
   </sheetData>
